--- a/data/trans_dic/P55$amigo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,91</t>
+          <t>0,0; 30,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,99</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>0,0; 10,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,63</t>
+          <t>0,6; 5,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,32</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,59</t>
+          <t>0,77; 4,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>0,0; 11,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,03</t>
+          <t>1,59; 15,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 10,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,92</t>
+          <t>2,64; 9,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,37</t>
+          <t>3,29; 9,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,98</t>
+          <t>0,0; 19,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 20,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,67</t>
+          <t>0,0; 19,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 24,29</t>
+          <t>2,03; 22,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,81</t>
+          <t>0,0; 13,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>0,0; 13,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 13,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 12,5</t>
+          <t>2,85; 12,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,07</t>
+          <t>1,07; 12,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,11</t>
+          <t>1,25; 11,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,77</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 12,4</t>
+          <t>3,32; 12,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>0,0; 11,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 13,02</t>
+          <t>1,21; 11,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,8</t>
+          <t>0,0; 9,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 12,15</t>
+          <t>3,91; 11,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,82</t>
+          <t>3,83; 10,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,12</t>
+          <t>0,71; 9,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,93</t>
+          <t>2,48; 8,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,04</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,73</t>
+          <t>0,36; 2,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,88</t>
+          <t>0,93; 5,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,48</t>
+          <t>3,63; 7,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,18</t>
+          <t>1,0; 3,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,36</t>
+          <t>0,74; 3,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,21</t>
+          <t>0,84; 4,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,78</t>
+          <t>3,72; 6,81</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10057</t>
+          <t>0; 10063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1606</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3462</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5816</t>
+          <t>0; 6372</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6746</t>
+          <t>0; 6011</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>477; 4489</t>
+          <t>477; 4516</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6543</t>
+          <t>0; 6644</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 9040</t>
+          <t>0; 10879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6107</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1057; 5934</t>
+          <t>1001; 5902</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4085</t>
+          <t>0; 5562</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2127</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1664</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>671; 5816</t>
+          <t>614; 6010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5651</t>
+          <t>0; 4723</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5537</t>
+          <t>0; 5523</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7471</t>
+          <t>0; 8152</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2256; 8529</t>
+          <t>2269; 8403</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6762</t>
+          <t>0; 6722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5463</t>
+          <t>0; 5626</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 8723</t>
+          <t>0; 7875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4032; 11689</t>
+          <t>4103; 11938</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4096</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5469</t>
+          <t>0; 5699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4576</t>
+          <t>0; 4570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>529; 6200</t>
+          <t>519; 5842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6416</t>
+          <t>0; 6379</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6399</t>
+          <t>0; 7053</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4791</t>
+          <t>0; 6992</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1220; 7291</t>
+          <t>1661; 7004</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>711; 7529</t>
+          <t>731; 8208</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>993; 8077</t>
+          <t>995; 9321</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6562</t>
+          <t>0; 7298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2456; 10395</t>
+          <t>2781; 10288</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1572</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1656</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>528; 5627</t>
+          <t>525; 5076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 5308</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2026</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9302</t>
+          <t>0; 7266</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4142; 12670</t>
+          <t>4079; 12325</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4652</t>
+          <t>0; 5006</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5175</t>
+          <t>0; 4242</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 7945</t>
+          <t>0; 8435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5155; 14481</t>
+          <t>5653; 15011</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6085</t>
+          <t>0; 6390</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1056; 14792</t>
+          <t>1039; 14098</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3529; 12456</t>
+          <t>3890; 12919</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2104; 11637</t>
+          <t>2066; 11894</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>992; 7624</t>
+          <t>994; 8357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3454; 15713</t>
+          <t>2478; 15565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12238; 24564</t>
+          <t>11911; 24099</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3620; 14944</t>
+          <t>3573; 13827</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3229; 18581</t>
+          <t>3156; 16662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3582; 16351</t>
+          <t>3260; 15803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17464; 32884</t>
+          <t>18037; 33050</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$amigo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,93</t>
+          <t>0,0; 30,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,07</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 12,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,67</t>
+          <t>0,64; 5,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,45</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,63</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,56</t>
+          <t>0,7; 4,26</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,58</t>
+          <t>0,0; 10,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 15,53</t>
+          <t>1,73; 14,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,61</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,77</t>
+          <t>2,69; 9,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,57</t>
+          <t>2,79; 9,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 19,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,4</t>
+          <t>0,0; 16,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,65</t>
+          <t>0,0; 16,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 22,88</t>
+          <t>1,72; 22,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,73</t>
+          <t>0,0; 13,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,59</t>
+          <t>0,0; 14,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,56</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,01</t>
+          <t>2,02; 11,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 12,06</t>
+          <t>1,1; 10,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,67</t>
+          <t>1,17; 10,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 8,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 12,27</t>
+          <t>2,91; 12,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,14</t>
+          <t>0,0; 14,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,74</t>
+          <t>1,15; 10,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,22</t>
+          <t>0,0; 9,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,82</t>
+          <t>3,85; 12,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,18</t>
+          <t>3,64; 11,25</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,64</t>
+          <t>0,71; 9,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,22</t>
+          <t>2,39; 7,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,91; 5,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,35; 3,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,82</t>
+          <t>0,92; 5,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,34</t>
+          <t>3,7; 7,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>0,91; 3,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,91</t>
+          <t>0,72; 3,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,06</t>
+          <t>0,92; 4,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,81</t>
+          <t>3,53; 6,74</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2938</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10063</t>
+          <t>0; 9962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 3137</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6372</t>
+          <t>0; 5806</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1675,32 +1675,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6011</t>
+          <t>0; 5456</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>477; 4516</t>
+          <t>544; 5067</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6644</t>
+          <t>0; 5782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 10879</t>
+          <t>0; 10889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4952</t>
+          <t>0; 7305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1001; 5902</t>
+          <t>965; 5869</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7463</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5562</t>
+          <t>0; 4973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1868,47 +1868,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>614; 6010</t>
+          <t>726; 6129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 4323</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5523</t>
+          <t>0; 5848</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 8152</t>
+          <t>0; 7501</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2269; 8403</t>
+          <t>2543; 9434</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6722</t>
+          <t>0; 6885</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5626</t>
+          <t>0; 7405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7875</t>
+          <t>0; 8716</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4103; 11938</t>
+          <t>3809; 12489</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6078</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4120</t>
+          <t>0; 4110</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5699</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4570</t>
+          <t>0; 3832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>519; 5842</t>
+          <t>512; 6624</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6379</t>
+          <t>0; 6318</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7053</t>
+          <t>0; 7313</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6992</t>
+          <t>0; 5940</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1661; 7004</t>
+          <t>1308; 7302</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>731; 8208</t>
+          <t>746; 7468</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>995; 9321</t>
+          <t>936; 8357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7298</t>
+          <t>0; 6664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2781; 10288</t>
+          <t>2757; 11583</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9961</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4459</t>
+          <t>0; 5986</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>525; 5076</t>
+          <t>510; 4778</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5308</t>
+          <t>0; 6059</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7266</t>
+          <t>0; 7365</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4079; 12325</t>
+          <t>4340; 14146</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5006</t>
+          <t>0; 4645</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4242</t>
+          <t>0; 5534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 8435</t>
+          <t>0; 7492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5653; 15011</t>
+          <t>5733; 17706</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>26440</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6390</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1039; 14098</t>
+          <t>1040; 13502</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3890; 12919</t>
+          <t>4040; 12583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2066; 11894</t>
+          <t>2095; 11614</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>994; 8357</t>
+          <t>985; 8554</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2478; 15565</t>
+          <t>2472; 14437</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11911; 24099</t>
+          <t>13233; 26954</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3573; 13827</t>
+          <t>3256; 14253</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3156; 16662</t>
+          <t>3047; 16801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3260; 15803</t>
+          <t>3582; 16601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18037; 33050</t>
+          <t>18597; 35462</t>
         </is>
       </c>
     </row>
